--- a/artfynd/A 948-2024 artfynd.xlsx
+++ b/artfynd/A 948-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115357415</v>
+        <v>115357359</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588394</v>
+        <v>588524</v>
       </c>
       <c r="R2" t="n">
-        <v>6425897</v>
+        <v>6426029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flög iväg från tall</t>
+          <t>Ring - vitt mycel under</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115357359</v>
+        <v>115357415</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,34 +800,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -845,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588524</v>
+        <v>588394</v>
       </c>
       <c r="R3" t="n">
-        <v>6426029</v>
+        <v>6425897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ring - vitt mycel under</t>
+          <t>Flög iväg från tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -910,6 +900,115 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115825623</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 938, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>588662</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6425961</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
